--- a/novy_excel.xlsx
+++ b/novy_excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\PycharmProjects\qr_generator-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0812227-3CEF-4F8E-B1B0-A56ACAEE4F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28F7C36-B8BB-4702-AC9D-E93196249EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2340,7 +2340,27 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
